--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -841,7 +841,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>601</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>602</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>603</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Round-round" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Loot-loot" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="RankReward-rank_reward" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cosmetic-cosmetic" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -841,7 +842,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>601</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -926,7 +927,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>602</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1011,7 +1012,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>603</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1105,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,6 +1200,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1291,6 +1297,11 @@
           <t>效果强度(按effect解释)</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>外观资产目录名(轮胎件指向art/tires/&lt;model&gt;/)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1381,6 +1392,11 @@
       <c r="R3" t="inlineStr">
         <is>
           <t>power</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -1447,6 +1463,7 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1511,6 +1528,7 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1575,6 +1593,7 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1639,6 +1658,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>slick_v1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1703,6 +1727,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>offroad_v1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1767,6 +1796,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>rain_v1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1831,6 +1865,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>allterrain_v1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1895,6 +1934,7 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1959,6 +1999,7 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2023,6 +2064,7 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2129,7 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2151,6 +2194,7 @@
       <c r="R15" t="n">
         <v>30</v>
       </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,6 +2259,7 @@
       <c r="R16" t="n">
         <v>0.5</v>
       </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2279,7 +2324,9 @@
       <c r="R17" t="n">
         <v>2</v>
       </c>
-    </row>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2291,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2310,11 +2357,6 @@
           <t>tr_string</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2332,11 +2374,6 @@
           <t>地图介绍</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>天气状态</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2352,11 +2389,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>desc</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>weather</t>
         </is>
       </c>
     </row>
@@ -2374,11 +2406,6 @@
           <t>Long straights under open sky, top-speed heaven.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>sunny</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2394,11 +2421,6 @@
           <t>Steep jumps and slippery dirt. Offroad tires and tough suspension shine.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sandstorm</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2414,11 +2436,6 @@
           <t>Storm-soaked tight corners. Rain tires and downforce prevail.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>storm</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2432,11 +2449,6 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Packed snow and ice; grip is everything.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>snow</t>
         </is>
       </c>
     </row>
@@ -3164,4 +3176,198 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tr_string</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tr_string</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>外观件名</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>稀有度</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>资产目录名</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>701</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sport Wheels V1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sport_v1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Box-spoke sport hub. Default look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>702</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Classic Wheels V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>classic_v1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Classic multi-spoke dish hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>703</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aero Wheels V1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>wheel</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>aero_v1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Smooth aero cover hub.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -842,7 +842,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>601</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>602</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>603</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1463,7 +1463,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1528,7 +1527,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1593,7 +1591,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1934,7 +1931,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1999,7 +1995,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,7 +2059,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2129,7 +2123,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2194,7 +2187,6 @@
       <c r="R15" t="n">
         <v>30</v>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2259,7 +2251,6 @@
       <c r="R16" t="n">
         <v>0.5</v>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,9 +2315,7 @@
       <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="inlineStr"/>
-    </row>
-    <row r="18"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,6 +585,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -712,6 +717,11 @@
           <t>转动惯量倍率</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>默认轮毂样式</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -837,6 +847,11 @@
       <c r="Y3" t="inlineStr">
         <is>
           <t>inertia_multiplier</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>wheel</t>
         </is>
       </c>
     </row>
@@ -924,6 +939,11 @@
       <c r="Y4" t="n">
         <v>1.3</v>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>sport_v1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1009,6 +1029,11 @@
       <c r="Y5" t="n">
         <v>1</v>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>sport_v1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1093,6 +1118,11 @@
       </c>
       <c r="Y6" t="n">
         <v>1.15</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>sport_v1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -2482,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2656,6 +2656,132 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>Loot pickup radius (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>checkpoint_interval</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Checkpoint spacing along main route (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rewind_speed_limit</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rewind (R) allowed below this speed (m/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rewind_ghost_sec</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ghost (translucent, no car collision) after rewind (sec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cam_chase_distance</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Chase cam distance (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cam_chase_height</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Chase cam height (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cam_fov_max</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>79</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Chase cam max FOV at top speed (deg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cam_shake</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Camera shake master switch (0=off)</t>
         </is>
       </c>
     </row>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -2482,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2785,6 +2785,79 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bump_strength</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Car-car impact boost multiplier (x closing speed x reduced mass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>bump_min_speed</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closing speed below this no boost (m/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>bump_max_speed</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closing speed cap for boost math (m/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>bump_yaw</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Yaw spin torque multiplier on corner hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -2482,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2849,15 +2849,69 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Yaw spin torque multiplier on corner hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bump_destab_speed</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closing speed to trigger destabilization window (m/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bump_destab_time</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Yaw spin torque multiplier on corner hits</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Max destabilization window duration (s, scales with closing speed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>bump_destab_grip</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tire friction scale during destabilization window</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,6 +1120,276 @@
         <v>1.15</v>
       </c>
       <c r="Z6" t="inlineStr">
+        <is>
+          <t>sport_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>701</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NPC Van (Traffic)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RWD</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>320</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NPC traffic target car; same physics params as player car 601, separate art id slot.</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>420</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3.6|2.2|1.6|1.25|1.0|0.8</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>sport_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>702</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NPC Compact (Traffic)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>260</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NPC traffic target car; same physics params as player car 602, separate art id slot.</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>260</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6800</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3.8|2.4|1.7|1.3|1.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>sport_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>703</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NPC Pickup (Traffic)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AWD</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>290</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NPC traffic target car; same physics params as player car 603, separate art id slot.</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>330</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3.7|2.3|1.65|1.28|1.0|0.82</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>40</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>sport_v1</t>
         </is>
@@ -2482,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2911,7 +3181,78 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>npc_count</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NPC traffic cars spawned per round</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>npc_hp</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NPC traffic car hit points</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>npc_speed_scale</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NPC cruise speed scale vs AI pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>npc_damage_coeff</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NPC collision damage per m/s closing speed above bump_min_speed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -2752,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NPC traffic cars spawned per round</t>
+          <t>NPC traffic cars per round (max; rolled within [npc_count_min, this])</t>
         </is>
       </c>
     </row>
@@ -3250,6 +3250,78 @@
       <c r="D27" t="inlineStr">
         <is>
           <t>NPC collision damage per m/s closing speed above bump_min_speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>npc_w_common</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>70</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NPC type spawn weight: common (701, npc_common loot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>npc_count_min</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NPC traffic cars per round (min for random density)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>npc_w_rare</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>25</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NPC type spawn weight: rare (702, npc_rare loot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>npc_w_elite</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NPC type spawn weight: elite (703, npc_elite loot)</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3591,6 +3663,84 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>npc_common</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>75|25|0|0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>engine|tires|aero|chassis|tactical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>npc_rare</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20|50|30|0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>engine|tires|aero|chassis|tactical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>npc_elite</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0|15|45|40</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>engine|tires|aero|chassis|tactical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
     </row>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -2752,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3322,6 +3322,114 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>NPC type spawn weight: elite (703, npc_elite loot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>drift_speed_min</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Min speed to enter/hold drift mode (m/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>drift_brake_scale</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Handbrake force scale while drifting (bite, not full lock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>drift_rear_grip</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rear lateral grip scale while drifting (front untouched)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>drift_slip_assist</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Steering slip assist threshold while drifting (rad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>drift_yaw_engage</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Yaw stability engage angle while drifting (dot domain, ~40deg max drift angle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>drift_yaw_kick</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Drift-entry yaw kick angular velocity (rad/s, x steering input)</t>
         </is>
       </c>
     </row>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,7 +899,7 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>420</v>
+        <v>580</v>
       </c>
       <c r="N4" t="n">
         <v>7500</v>
@@ -989,7 +989,7 @@
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="N5" t="n">
         <v>6800</v>
@@ -1079,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>330</v>
+        <v>540</v>
       </c>
       <c r="N6" t="n">
         <v>7000</v>
@@ -1169,7 +1169,7 @@
         <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>420</v>
+        <v>580</v>
       </c>
       <c r="N7" t="n">
         <v>7500</v>
@@ -1259,7 +1259,7 @@
         <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="N8" t="n">
         <v>6800</v>
@@ -1349,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>330</v>
+        <v>540</v>
       </c>
       <c r="N9" t="n">
         <v>7000</v>
@@ -1395,6 +1395,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/data/ModRacer.xlsx
+++ b/config/data/ModRacer.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,7 +1395,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2753,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3246,11 +3245,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NPC collision damage per m/s closing speed above bump_min_speed</t>
+          <t>NPC collision damage scale on speed fraction (100km/h=50% hp, 200km/h=wreck, floor 25% per hit)</t>
         </is>
       </c>
     </row>
@@ -3431,6 +3430,186 @@
       <c r="D37" t="inlineStr">
         <is>
           <t>Drift-entry yaw kick angular velocity (rad/s, x steering input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>skid_lat_slip</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Lateral slip angle threshold for tire marks (rad, ~11.5deg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>skid_lon_slip</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Longitudinal slip threshold for tire marks (lockup/wheelspin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>skid_lifetime</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tire mark fade-out duration (sec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>skid_alpha</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tire mark peak opacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>skid_gap</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Min segment length between mark quads (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>skid_pool</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ring buffer segments per car (oldest overwritten)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>env_clouds_enabled</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Volumetric cloud sky master switch (clayjohn raymarch sky shader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>env_cloud_coverage</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Base cloud coverage 0.1-1 (per-weather preset multiplies on top)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>env_cloud_density</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Base cloud density (absorption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>env_cloud_wind</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Cloud wind speed</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3653,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3501,6 +3685,11 @@
           <t>候选地图id</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>名次积分表(名次1起,超长按0,决赛加码供翻盘)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3528,6 +3717,11 @@
           <t>map_pool</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3547,6 +3741,11 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>1|2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3|2|1|0|0|0|0|0</t>
         </is>
       </c>
     </row>
@@ -3570,6 +3769,11 @@
           <t>2|3</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3|2|1|0|0|0|0|0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3591,6 +3795,11 @@
           <t>3|4</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3|2|1|0|0|0|0|0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3612,7 +3821,13 @@
           <t>1|2|3|4</t>
         </is>
       </c>
-    </row>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12|8|4|0|0|0|0|0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
